--- a/rules/CORE-002115/negative/01/data/CORE-002115-negative-1.xlsx
+++ b/rules/CORE-002115/negative/01/data/CORE-002115-negative-1.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>SSDTC</t>
+          <t>SSTDTC</t>
         </is>
       </c>
     </row>
